--- a/backtest_runs/20260410_193731/by_symbol/PAKD/PAKD.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/PAKD/PAKD.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>100000</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>100000</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>100000</v>
@@ -955,7 +955,7 @@
         <v>-5357.300000000003</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>94642.7</v>
@@ -1001,7 +1001,7 @@
         <v>-650.6499999999967</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>93992.05</v>
@@ -1093,7 +1093,7 @@
         <v>-1706.899999999997</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>92285.15000000001</v>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>92285.15000000001</v>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>92285.15000000001</v>
@@ -1231,7 +1231,7 @@
         <v>-59.15000000000624</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>92226</v>
@@ -1277,7 +1277,7 @@
         <v>-2408.249999999995</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>89817.75</v>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>90561.35000000001</v>
@@ -1461,7 +1461,7 @@
         <v>-3794.050000000007</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>88195.35000000001</v>
@@ -1553,7 +1553,7 @@
         <v>-2120.950000000004</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>88034.8</v>
@@ -1645,7 +1645,7 @@
         <v>-3870.099999999999</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>91440.15000000001</v>
